--- a/mis-portal/reports/2026-06-08/SDR_20260608.xlsx
+++ b/mis-portal/reports/2026-06-08/SDR_20260608.xlsx
@@ -19,9 +19,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD-MMM-YYYY"/>
-    <numFmt numFmtId="166" formatCode="₹#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="DD-MMM-YYYY"/>
+    <numFmt numFmtId="165" formatCode="₹#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -84,12 +84,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -140,32 +140,35 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,9 +176,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -649,554 +649,724 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MF — Debt / Liquid Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ICICI Prudential All Seasons Bond Fund - Growth</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>4146387.51</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>5158109.34</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5158109.3427</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>5141626.49</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>16482.85</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>78915.84</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1011721.83</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>0.015537</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>0.244001</v>
+      </c>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Total MF Debt / Liquid</t>
+        </is>
+      </c>
+      <c r="C6" s="10">
+        <f>SUM(C5:C5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="10">
+        <f>SUM(D5:D5)</f>
+        <v/>
+      </c>
+      <c r="E6" s="10">
+        <f>SUM(E5:E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="10">
+        <f>SUM(F5:F5)</f>
+        <v/>
+      </c>
+      <c r="G6" s="10">
+        <f>SUM(G5:G5)</f>
+        <v/>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(H5:H5)</f>
+        <v/>
+      </c>
+      <c r="I6" s="10">
+        <f>SUM(I5:I5)</f>
+        <v/>
+      </c>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>A. TOTAL FIXED INCOME</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>MF — Equity Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Dynamic Asset Allocation Active FOF-Growth (formerly ICICI Prudential Advisor Series</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>7781864.58</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>7781864.5805</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>7815024.79</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-33160.21</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>381265.27</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>4081864.58</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.05151799999999999</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>1.103207</v>
+      </c>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Total MF — Equity Funds</t>
+        </is>
+      </c>
+      <c r="C12" s="10">
+        <f>SUM(C11:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="10">
+        <f>SUM(D11:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="10">
+        <f>SUM(E11:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="10">
+        <f>SUM(F11:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="10">
+        <f>SUM(G11:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="10">
+        <f>SUM(H11:H11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="10">
+        <f>SUM(I11:I11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="11" t="n"/>
+      <c r="M12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Direct Equities</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C14" s="6" t="n">
         <v>42973</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D14" s="6" t="n">
         <v>26669.5</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E14" s="6" t="n">
         <v>26247</v>
       </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n">
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n">
         <v>-16726</v>
       </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n">
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n">
         <v>-0.3892</v>
       </c>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>CCAVENUE</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>CCAVENUE  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
         <v>46181</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <v>59258.49</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>41340</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <v>41400</v>
       </c>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n">
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n">
         <v>-17858.49</v>
       </c>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="14" t="n">
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="15" t="n">
         <v>-0.3014</v>
       </c>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="15" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>GLOBUSSPR</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
+      <c r="L15" s="15" t="n"/>
+      <c r="M15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>GLOBUSSPR  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C16" s="6" t="n">
         <v>40259.3</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D16" s="6" t="n">
         <v>85100</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E16" s="6" t="n">
         <v>84330</v>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n">
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n">
         <v>44070.7</v>
       </c>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n">
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n">
         <v>1.0947</v>
       </c>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>GOLDBEES</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>GOLDBEES  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
         <v>46181</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>472706.43</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>869400</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E17" s="14" t="n">
         <v>870030</v>
       </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n">
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n">
         <v>397323.57</v>
       </c>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="14" t="n">
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="n">
         <v>0.8405</v>
       </c>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="15" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>GOLDIETF</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>GOLDIETF  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C18" s="6" t="n">
         <v>206896.42</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D18" s="6" t="n">
         <v>513800</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E18" s="6" t="n">
         <v>514200</v>
       </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n">
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n">
         <v>307303.58</v>
       </c>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n">
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n">
         <v>1.4853</v>
       </c>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>HAL  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
         <v>46181</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>55660</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>42102</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E19" s="14" t="n">
         <v>42280</v>
       </c>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="13" t="n">
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n">
         <v>-13380</v>
       </c>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="14" t="n">
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n">
         <v>-0.2404</v>
       </c>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="15" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>46181</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>42941</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>42879.6</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>42732</v>
-      </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n">
-        <v>-209</v>
-      </c>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n">
-        <v>-0.0049</v>
-      </c>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>JIOFIN</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>46181</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>150510</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>150767.5</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>148297.5</v>
-      </c>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n">
-        <v>-2212.5</v>
-      </c>
-      <c r="J15" s="14" t="n"/>
-      <c r="K15" s="14" t="n">
-        <v>-0.0147</v>
-      </c>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>46181</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>35498.3</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>76205</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>75200</v>
-      </c>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n">
-        <v>39701.7</v>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n">
-        <v>1.1184</v>
-      </c>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>46181</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>37352</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>117111</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>116040</v>
-      </c>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n">
-        <v>78688</v>
-      </c>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="14" t="n">
-        <v>2.1067</v>
-      </c>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="15" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>NATIONALUM</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>46181</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>29052.9</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>61680</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>60176</v>
-      </c>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n">
-        <v>31123.1</v>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n">
-        <v>1.0713</v>
-      </c>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>POLYCAB</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>46181</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>50894</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>288120</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>283620</v>
-      </c>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n">
-        <v>232726</v>
-      </c>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="14" t="n">
-        <v>4.5728</v>
-      </c>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="15" t="inlineStr"/>
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Total Direct Equities</t>
-        </is>
-      </c>
-      <c r="C20" s="16">
-        <f>SUM(C8:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="16">
-        <f>SUM(D8:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="16">
-        <f>SUM(E8:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="16">
-        <f>SUM(F8:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="16">
-        <f>SUM(G8:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="16">
-        <f>SUM(H8:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="16">
-        <f>SUM(I8:I19)</f>
-        <v/>
-      </c>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
+          <t>INFY  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>42941</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>42879.6</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>42732</v>
+      </c>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n">
+        <v>-209</v>
+      </c>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>B. TOTAL EQUITY</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>ALTERNATES</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>JIOFIN  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>150510</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>150767.5</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>148297.5</v>
+      </c>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n">
+        <v>-2212.5</v>
+      </c>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="n">
+        <v>-0.0147</v>
+      </c>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>KPITTECH  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>35498.3</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>76205</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>75200</v>
+      </c>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n">
+        <v>39701.7</v>
+      </c>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n">
+        <v>1.1184</v>
+      </c>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>LT  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>37352</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>117111</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>116040</v>
+      </c>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n">
+        <v>78688</v>
+      </c>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="n">
+        <v>2.1067</v>
+      </c>
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>NATIONALUM  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>29052.9</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>61680</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>60176</v>
+      </c>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n">
+        <v>31123.1</v>
+      </c>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="7" t="n">
+        <v>1.0713</v>
+      </c>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>POLYCAB  [zerodha]</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>50894</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>288120</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>283620</v>
+      </c>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n">
+        <v>232726</v>
+      </c>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="15" t="n">
+        <v>4.5728</v>
+      </c>
+      <c r="L25" s="15" t="n"/>
+      <c r="M25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Total Direct Equities</t>
+        </is>
+      </c>
+      <c r="C26" s="10">
+        <f>SUM(C14:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="10">
+        <f>SUM(D14:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>SUM(E14:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="10">
+        <f>SUM(F14:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="10">
+        <f>SUM(G14:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="10">
+        <f>SUM(H14:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="10">
+        <f>SUM(I14:I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="11" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>B. TOTAL EQUITY</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ALTERNATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
           <t>D. TOTAL ALTERNATES</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>E. Funds in Transit</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>F. Broker Balance</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>G. Funds in Bank</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>H. GRAND TOTAL (A+B+D+E+F+G)</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>Report generated on 08 Jun 2026 10:06 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="11" t="n"/>
+      <c r="J38" s="11" t="n"/>
+      <c r="K38" s="11" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Report generated on 08 Jun 2026 11:25 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A24:B24"/>
+  <mergeCells count="18">
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A36:M36"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A34:M34"/>
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A40:M40"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A30:M30"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
